--- a/data/trans_orig/IP07_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108353</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>99517</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>117065</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>99188</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>90736</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>107450</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>90106</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>107763</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>108353</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>98950</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194450</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218325</t>
+          <t>219162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43905</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35193</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>52741</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39538</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31276</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47990</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30963</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48620</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43905</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34978</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>53308</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72659</t>
+          <t>71822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96534</t>
+          <t>95995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>152258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>152258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>153638</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143647</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>163415</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>142634</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>133069</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>152013</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>132878</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>151129</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>73,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>153638</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>142917</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>163791</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281753</t>
+          <t>282528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310018</t>
+          <t>310465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57157</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47380</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67148</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>52529</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43150</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62094</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44034</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>62285</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>26,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>57157</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47004</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>67878</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95940</t>
+          <t>95493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124205</t>
+          <t>123430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210795</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124378</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116041</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>131265</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110101</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>101464</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116448</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>102502</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>116779</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>79,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>124378</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>115965</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>130666</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223479</t>
+          <t>223492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244266</t>
+          <t>245448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25279</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18392</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33616</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27716</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21369</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36353</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21038</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35315</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25279</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33692</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63995</t>
+          <t>63982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>165656</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>155452</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>174790</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>176549</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>166760</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>184640</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>166581</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>184054</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>84,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>165656</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>155968</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>174600</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327536</t>
+          <t>328777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>354381</t>
+          <t>354712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41524</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32390</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51728</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32766</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24675</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42555</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25261</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42734</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>15,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41524</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>32580</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>51212</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62114</t>
+          <t>61783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88959</t>
+          <t>87718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207180</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>552024</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>531032</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>569418</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>510969</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>544993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>509734</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>544114</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>552024</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>533092</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>570402</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1055193</t>
+          <t>1057138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1105701</t>
+          <t>1107039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>167866</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>150472</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>188858</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>152550</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>136028</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>170052</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>136907</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>171287</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>22,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>167866</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>149488</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>186798</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295210</t>
+          <t>293872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345718</t>
+          <t>343773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>119801</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>111039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>127975</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>108558</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>100007</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>115860</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>99494</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>115796</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>119801</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>111026</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>128488</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215729</t>
+          <t>216547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238624</t>
+          <t>240381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34044</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25870</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42806</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30063</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22761</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38614</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22825</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39127</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34044</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25357</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>42819</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138621</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>158826</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146774</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>168772</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>145841</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>135155</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>155783</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>135482</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>156088</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>70,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>158826</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>147711</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>169968</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289716</t>
+          <t>290002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319512</t>
+          <t>320085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63570</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53624</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75622</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>60517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50575</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71203</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50270</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>70876</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63570</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>52428</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74685</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>28,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109242</t>
+          <t>108669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139038</t>
+          <t>138752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222396</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132258</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122931</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140495</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>119524</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109795</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>127090</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>109829</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>127380</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>77,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>132258</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>124056</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>140516</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>79,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239084</t>
+          <t>239053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>263279</t>
+          <t>262770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34334</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26097</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43661</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>35154</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27588</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44883</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27298</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>22,73%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34334</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26076</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>42536</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82186</t>
+          <t>82217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154678</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>149431</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>137299</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>159691</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>72,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>159716</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>149550</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>169555</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>148623</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>168782</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>149431</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>138054</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>159621</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>72,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293650</t>
+          <t>292607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324115</t>
+          <t>322842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47322</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69714</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49797</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39958</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40731</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60890</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>57582</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>68959</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92412</t>
+          <t>93685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122877</t>
+          <t>123920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207013</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209513</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207013</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>560316</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>539212</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>577892</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>77,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>770</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>514352</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>551741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>513145</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>553843</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>560316</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>538961</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>579701</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1065909</t>
+          <t>1066253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1119379</t>
+          <t>1120739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>189530</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>171954</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>210634</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>175531</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>157429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>194818</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>155327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>196025</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>189530</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>170145</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>210885</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339637</t>
+          <t>338277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393107</t>
+          <t>392763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>122452</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>114250</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129299</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>115924</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>109473</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>121966</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>108557</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>122172</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>87,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>122452</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>113282</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>129871</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227307</t>
+          <t>227452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248146</t>
+          <t>247366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24856</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18009</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33058</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17101</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11059</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23552</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24468</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24856</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17437</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34026</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>52882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147308</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133025</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>191014</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>181701</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>198722</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>177414</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>168805</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>184774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>168342</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>183980</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>86,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>191014</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>182472</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>199631</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356489</t>
+          <t>354559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379378</t>
+          <t>378780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31939</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24231</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41252</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28683</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21323</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37292</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22117</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37755</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>31939</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23322</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40481</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72561</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222953</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206097</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222953</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>133285</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>147466</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>129093</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>141541</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>129653</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>141956</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>87,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>133144</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>148366</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267565</t>
+          <t>267349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286031</t>
+          <t>285585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25604</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19207</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33388</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18604</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13090</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25538</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12675</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24978</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>12,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25604</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18307</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33529</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53739</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154631</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>182902</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>174579</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>189383</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>180761</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>172324</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>187784</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>171730</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>188247</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>87,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>83,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>182902</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>173684</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>189456</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352086</t>
+          <t>351520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374097</t>
+          <t>372983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22188</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15707</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30511</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>25258</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18235</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33695</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17772</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34289</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>22188</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15634</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31406</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37013</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59024</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205090</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206019</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>621765</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>653037</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>592800</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>623724</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>595178</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>622956</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>84,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>620838</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>653042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1226851</t>
+          <t>1226504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1267830</t>
+          <t>1268462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>104588</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88987</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120259</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>89645</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76049</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>106973</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>104595</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>104588</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>88982</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>121186</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173967</t>
+          <t>173335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214946</t>
+          <t>215293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es muy buena o excelente en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82953</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62894</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>94496</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89128</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>81524</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96285</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>69,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>94120</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71724</t>
+          <t>84088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107354</t>
+          <t>98557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>175312</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155824</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196977</t>
+          <t>189343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42953</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63012</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28152</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20995</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35756</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33058</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>74445</t>
+          <t>71665</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>91293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>175775</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>163112</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>188427</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>141305</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>125427</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>151463</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>192454</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178780</t>
+          <t>128617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203639</t>
+          <t>148772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>333760</t>
+          <t>315487</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313174</t>
+          <t>298767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348637</t>
+          <t>330276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61431</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74094</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>49207</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39049</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65085</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76255</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>111788</t>
+          <t>106132</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96911</t>
+          <t>91343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132374</t>
+          <t>122852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>134309</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124597</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>158254</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>147691</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>172721</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>145571</t>
+          <t>124619</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132304</t>
+          <t>115256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155535</t>
+          <t>133004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>303825</t>
+          <t>258929</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286215</t>
+          <t>246330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321704</t>
+          <t>270943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32147</t>
+          <t>34032</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>71862</t>
+          <t>66462</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53983</t>
+          <t>54448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89472</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>137683</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>128501</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>145290</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>126158</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>115888</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>134657</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>75,11%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147534</t>
+          <t>124555</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137762</t>
+          <t>114602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155855</t>
+          <t>133856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>273693</t>
+          <t>262238</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261218</t>
+          <t>249262</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285658</t>
+          <t>274463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31693</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24086</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40875</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41804</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33305</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52074</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>42590</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>52543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>74283</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>62058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>87259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>503826</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>550622</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>514845</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>493501</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>538549</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>481245</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>546755</t>
+          <t>462596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>600807</t>
+          <t>497545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1094524</t>
+          <t>1011965</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1056234</t>
+          <t>977554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1124260</t>
+          <t>1039155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>170109</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>150207</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>197003</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>151310</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>127606</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>172654</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182293</t>
+          <t>148433</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161165</t>
+          <t>132133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>167082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>333603</t>
+          <t>318543</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303867</t>
+          <t>291353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>371893</t>
+          <t>352954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
